--- a/sources/ling_step8b.xlsx
+++ b/sources/ling_step8b.xlsx
@@ -889,14 +889,19 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RDS f,f+3+4</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RDS f,f+3+4</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -961,14 +966,19 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RDS f,f+1+3</t>
+          <t>f,f+1+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RDS f,f+1+3</t>
+          <t>f,f+1+3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1038,14 +1048,19 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AOP 1+3 [~D]</t>
+          <t>1+3 [~D]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AOP 1+3 [~D]</t>
+          <t>1+3 [~D]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/sources/ling_step8b.xlsx
+++ b/sources/ling_step8b.xlsx
@@ -426,7 +426,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col hidden="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col hidden="1" min="10" max="10"/>
@@ -11530,22 +11530,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>(~B)RDS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11632,22 +11637,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>(~U)Quick roll to background; (~D)Quick roll to foreground</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12546,12 +12556,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
@@ -12633,7 +12643,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">

--- a/sources/ling_step8b.xlsx
+++ b/sources/ling_step8b.xlsx
@@ -1108,6 +1108,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -1175,6 +1180,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -1237,6 +1247,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1297,6 +1312,11 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -12853,6 +12873,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -12898,6 +12923,11 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
